--- a/data/trans_bre/P1403-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1403-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-8,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-41,81%</t>
+          <t>-38,47%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,58</t>
+          <t>-5,48; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,86; -0,8</t>
+          <t>-11,69; -1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,59</t>
+          <t>-9,23; 0,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; -4,83</t>
+          <t>-12,31; -4,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 39,37</t>
+          <t>-42,59; 37,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,62; -5,26</t>
+          <t>-63,55; -6,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 8,36</t>
+          <t>-59,34; 5,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,3; -25,65</t>
+          <t>-51,98; -21,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,31</t>
+          <t>-7,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-39,23%</t>
+          <t>-35,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -2,71</t>
+          <t>-10,45; -2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,3</t>
+          <t>-7,88; 2,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -1,57</t>
+          <t>-11,28; -1,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; -3,8</t>
+          <t>-12,04; -3,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,6; -25,56</t>
+          <t>-73,73; -20,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 22,33</t>
+          <t>-52,77; 19,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,01; -11,39</t>
+          <t>-65,12; -11,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,39; -19,45</t>
+          <t>-49,39; -18,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,41</t>
+          <t>-6,23; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,75</t>
+          <t>-4,86; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 12,59</t>
+          <t>-3,37; 11,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 24,86</t>
+          <t>-3,18; 9,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 47,27</t>
+          <t>-43,2; 51,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 40,72</t>
+          <t>-21,08; 36,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 84,71</t>
+          <t>-17,93; 77,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 434,15</t>
+          <t>-13,51; 49,31</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>-26,01%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,58</t>
+          <t>-5,8; 0,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -5,03</t>
+          <t>-11,73; -4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -4,11</t>
+          <t>-10,16; -3,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 43,99</t>
+          <t>-8,44; -2,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 4,13</t>
+          <t>-32,02; 4,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,14; -28,11</t>
+          <t>-56,46; -27,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,9; -24,32</t>
+          <t>-52,39; -21,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 225,8</t>
+          <t>-37,15; -11,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,04</t>
+          <t>-1,51; 7,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 11,55</t>
+          <t>1,78; 11,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,96</t>
+          <t>-1,46; 6,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 10,32</t>
+          <t>4,91; 12,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 83,62</t>
+          <t>-10,1; 75,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 74,48</t>
+          <t>7,74; 74,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 48,64</t>
+          <t>-7,96; 45,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 55,06</t>
+          <t>22,53; 77,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,73</t>
+          <t>26,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1484,69%</t>
+          <t>1410,8%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,48; 26,17</t>
+          <t>20,57; 25,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,62; 33,27</t>
+          <t>26,73; 33,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,48; 29,71</t>
+          <t>23,45; 29,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,6; 31,0</t>
+          <t>23,54; 29,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>619,36; 4221,95</t>
+          <t>632,25; 4311,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>819,22; 8376,05</t>
+          <t>708,27; 8188,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>970,92; —</t>
+          <t>1078,81; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>635,72; 3651,7</t>
+          <t>605,65; 3414,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,33</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,72</t>
+          <t>2,09; 5,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,19</t>
+          <t>2,27; 6,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,34</t>
+          <t>0,77; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 22,49</t>
+          <t>0,16; 3,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,8; 46,15</t>
+          <t>15,09; 45,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,17; 38,32</t>
+          <t>12,74; 38,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 30,42</t>
+          <t>4,51; 30,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,3; 127,3</t>
+          <t>0,82; 20,15</t>
         </is>
       </c>
     </row>
